--- a/TEMPLATE FORM PERAWANAN.xlsx
+++ b/TEMPLATE FORM PERAWANAN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26780681-36A5-444C-9FC6-C64536E3628B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AAD12E-4B20-4EEC-9CDC-B1A5A864FA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,6 +122,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -480,9 +483,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -523,6 +523,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -973,14 +976,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1"/>
@@ -1031,14 +1034,14 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="36"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="35"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
@@ -1075,7 +1078,7 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="12"/>
@@ -1088,7 +1091,7 @@
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="31" t="s">
         <v>16</v>
       </c>
       <c r="B11" s="12"/>
@@ -1101,7 +1104,7 @@
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="31" t="s">
         <v>17</v>
       </c>
       <c r="B12" s="12"/>
@@ -1114,7 +1117,7 @@
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="31" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="12"/>
@@ -1127,7 +1130,7 @@
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="31" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="12"/>
@@ -1140,7 +1143,7 @@
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="31" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="12"/>
@@ -1153,7 +1156,7 @@
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="31" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="12"/>
@@ -1166,7 +1169,7 @@
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="31" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="12"/>
@@ -1179,7 +1182,7 @@
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="31" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="12"/>
@@ -1506,126 +1509,126 @@
       <c r="A42" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="36">
         <f t="shared" ref="B42:F42" si="1">B41/31/24*100%</f>
         <v>0</v>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1"/>
-      <c r="B44" s="24"/>
+      <c r="B44" s="23"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="25"/>
+      <c r="F44" s="24"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1"/>
-      <c r="B45" s="24"/>
+      <c r="B45" s="23"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="26" t="s">
+      <c r="D45" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1"/>
-      <c r="B46" s="24"/>
+      <c r="B46" s="23"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="27"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B47" s="24"/>
+      <c r="B47" s="23"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="26" t="s">
+      <c r="D47" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E47" s="27"/>
-      <c r="F47" s="28"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1"/>
-      <c r="B48" s="24"/>
+      <c r="B48" s="23"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="27"/>
-      <c r="F48" s="28"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="27"/>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1"/>
-      <c r="B49" s="24"/>
+      <c r="B49" s="23"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="1"/>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1"/>
-      <c r="B50" s="24"/>
+      <c r="B50" s="23"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="27"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="26"/>
       <c r="F50" s="1"/>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1"/>
-      <c r="B51" s="24"/>
+      <c r="B51" s="23"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="27"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
       <c r="F51" s="1"/>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1"/>
-      <c r="B52" s="24"/>
+      <c r="B52" s="23"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="27"/>
-      <c r="F52" s="30"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="29"/>
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="1"/>
-      <c r="B53" s="24"/>
+      <c r="B53" s="23"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="26" t="s">
+      <c r="D53" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="E53" s="27"/>
-      <c r="F53" s="28"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="2">
